--- a/data/trans_dic/IP19C05-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C05-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis</t>
+          <t>Menores que en su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,04</t>
+          <t>0,0; 6,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,57</t>
+          <t>0,0; 5,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,22</t>
+          <t>0,84; 7,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,9</t>
+          <t>1,13; 10,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,68</t>
+          <t>0,94; 5,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,15</t>
+          <t>1,15; 6,74</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,6</t>
+          <t>0,54; 5,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,62</t>
+          <t>0,55; 5,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,13</t>
+          <t>1,21; 7,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,45</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 7,1</t>
+          <t>1,2; 6,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,53</t>
+          <t>0,0; 3,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,02</t>
+          <t>0,29; 2,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,61</t>
+          <t>1,19; 4,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,83</t>
+          <t>0,85; 3,82</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,58</t>
+          <t>0,0; 4,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 11,01</t>
+          <t>1,79; 9,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,4</t>
+          <t>0,0; 5,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,2</t>
+          <t>0,0; 4,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,6</t>
+          <t>0,0; 5,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,03</t>
+          <t>0,0; 2,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,76</t>
+          <t>0,72; 5,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,78</t>
+          <t>0,43; 3,74</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,58</t>
+          <t>0,0; 4,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,6</t>
+          <t>0,82; 7,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,37</t>
+          <t>0,66; 6,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,5</t>
+          <t>0,72; 6,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,75</t>
+          <t>0,0; 4,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,85</t>
+          <t>0,47; 3,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,78</t>
+          <t>0,4; 3,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,41</t>
+          <t>0,68; 4,36</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,09</t>
+          <t>0,36; 2,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,47</t>
+          <t>1,42; 4,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,15</t>
+          <t>1,36; 4,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,19</t>
+          <t>0,36; 2,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,1</t>
+          <t>0,78; 3,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,1</t>
+          <t>0,8; 3,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,74</t>
+          <t>0,52; 1,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,18</t>
+          <t>1,37; 3,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,12</t>
+          <t>1,37; 3,15</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,43%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2215</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3709</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4601</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4529</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3879</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>634; 5821</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>855; 8258</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1405; 8273</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1685; 9884</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1882</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1925</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3773</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4003</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5928</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4390</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>595; 5552</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>616; 5787</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1294; 7585</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3780</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1380; 7979</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3705</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>642; 5918</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2712; 11067</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1839; 8238</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3403</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1386</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1274</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3403</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2145</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3122</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1337; 7442</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4253</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3221</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4125</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3855</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1108; 7917</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>655; 5703</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2464</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2644</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2204</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1477</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3077</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2464</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4121</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3847</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>760; 6903</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721; 7531</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>647; 5831</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5088</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>870; 7170</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>748; 6682</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1468; 9413</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3387</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9286</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6153</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6918</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>15504</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>15257</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1266; 7840</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5024; 15210</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4915; 15038</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1317; 7925</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2840; 11182</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2928; 11394</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3691; 12639</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>9897; 23270</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>10024; 23039</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C05-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C05-Habitat-trans_dic.xlsx
@@ -683,12 +683,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 6,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,48</t>
+          <t>0,0; 6,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,74</t>
+          <t>0,84; 8,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 10,89</t>
+          <t>1,1; 9,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,55</t>
+          <t>0,93; 5,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,74</t>
+          <t>1,34; 7,14</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,04</t>
+          <t>0,54; 4,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,14</t>
+          <t>0,54; 5,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,08</t>
+          <t>1,22; 7,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 2,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,96</t>
+          <t>1,7; 7,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,41</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,67</t>
+          <t>0,29; 2,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,87</t>
+          <t>1,17; 4,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,82</t>
+          <t>0,87; 3,97</t>
         </is>
       </c>
     </row>
@@ -898,22 +898,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,51</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 9,99</t>
+          <t>1,5; 9,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,63</t>
+          <t>0,0; 6,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,14</t>
+          <t>0,0; 4,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,37</t>
+          <t>0,0; 4,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,62</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,13</t>
+          <t>0,73; 4,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,74</t>
+          <t>0,43; 3,84</t>
         </is>
       </c>
     </row>
@@ -1008,22 +1008,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,01</t>
+          <t>0,0; 5,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,42</t>
+          <t>0,8; 7,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,91</t>
+          <t>0,67; 7,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,48</t>
+          <t>0,71; 6,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,77</t>
+          <t>0,0; 4,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,85</t>
+          <t>0,38; 4,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,53</t>
+          <t>0,39; 3,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,36</t>
+          <t>0,69; 4,08</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,23</t>
+          <t>0,35; 2,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,3</t>
+          <t>1,49; 4,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,15</t>
+          <t>1,45; 4,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,19</t>
+          <t>0,36; 2,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,06</t>
+          <t>0,78; 3,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,1</t>
+          <t>0,78; 3,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,77</t>
+          <t>0,49; 1,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,23</t>
+          <t>1,35; 3,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,15</t>
+          <t>1,24; 3,15</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4529</t>
+          <t>0; 4620</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3879</t>
+          <t>0; 4548</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>634; 5821</t>
+          <t>629; 6119</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>855; 8258</t>
+          <t>836; 7467</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1405; 8273</t>
+          <t>1390; 8005</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1685; 9884</t>
+          <t>1965; 10463</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>595; 5552</t>
+          <t>596; 5058</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>616; 5787</t>
+          <t>608; 5890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1294; 7585</t>
+          <t>1304; 8101</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3780</t>
+          <t>0; 2891</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1380; 7979</t>
+          <t>1946; 8343</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3705</t>
+          <t>0; 3060</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>642; 5918</t>
+          <t>644; 6388</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2712; 11067</t>
+          <t>2665; 10747</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1839; 8238</t>
+          <t>1868; 8570</t>
         </is>
       </c>
     </row>
@@ -1743,22 +1743,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3122</t>
+          <t>0; 2646</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1337; 7442</t>
+          <t>1117; 7041</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4253</t>
+          <t>0; 4894</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3221</t>
+          <t>0; 3599</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1768,22 +1768,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4125</t>
+          <t>0; 3347</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3855</t>
+          <t>0; 3885</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1108; 7917</t>
+          <t>1121; 7545</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>655; 5703</t>
+          <t>656; 5847</t>
         </is>
       </c>
     </row>
@@ -1906,22 +1906,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3847</t>
+          <t>0; 5147</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>760; 6903</t>
+          <t>742; 6605</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>721; 7531</t>
+          <t>729; 7629</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>647; 5831</t>
+          <t>643; 5651</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1931,22 +1931,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5088</t>
+          <t>0; 5181</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>870; 7170</t>
+          <t>709; 7572</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>748; 6682</t>
+          <t>746; 6567</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1468; 9413</t>
+          <t>1491; 8803</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1266; 7840</t>
+          <t>1237; 7453</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5024; 15210</t>
+          <t>5259; 15848</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4915; 15038</t>
+          <t>5262; 16245</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1317; 7925</t>
+          <t>1299; 8508</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2840; 11182</t>
+          <t>2848; 11619</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2928; 11394</t>
+          <t>2859; 11704</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3691; 12639</t>
+          <t>3505; 12640</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9897; 23270</t>
+          <t>9716; 22836</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10024; 23039</t>
+          <t>9037; 23031</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C05-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C05-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,27 +630,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,84%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,25</t>
+          <t>0,84; 8,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,42</t>
+          <t>1,12; 9,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,13</t>
+          <t>0,0; 7,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 9,85</t>
+          <t>0,0; 6,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,37</t>
+          <t>0,94; 5,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 7,14</t>
+          <t>1,08; 6,15</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>1,71%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1,71%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,52%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,45</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1,7; 7,1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,53</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>0,54; 4,6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,54; 5,23</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,22; 7,56</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,59</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 7,27</t>
+          <t>0,54; 4,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>1,67; 7,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,88</t>
+          <t>0,29; 3,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,73</t>
+          <t>1,19; 4,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,97</t>
+          <t>0,86; 3,83</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4,57%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,83%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,82</t>
+          <t>0,0; 4,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 9,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,47</t>
+          <t>0,0; 6,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,62</t>
+          <t>0,0; 4,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,76; 11,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,35</t>
+          <t>0,0; 6,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 3,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,89</t>
+          <t>0,72; 4,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,84</t>
+          <t>0,43; 3,78</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2,65%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,43%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,36</t>
+          <t>0,71; 6,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 7,0</t>
+          <t>0,0; 4,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,28</t>
+          <t>0,0; 4,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,8; 7,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,85</t>
+          <t>0,67; 6,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,07</t>
+          <t>0,38; 3,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,47</t>
+          <t>0,39; 3,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,08</t>
+          <t>0,68; 4,41</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,62%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,51%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,12</t>
+          <t>0,37; 2,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,48</t>
+          <t>0,77; 3,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,48</t>
+          <t>0,66; 3,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,35</t>
+          <t>0,36; 2,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,17</t>
+          <t>1,51; 4,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,18</t>
+          <t>1,4; 4,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,77</t>
+          <t>0,48; 1,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,17</t>
+          <t>1,42; 3,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,15</t>
+          <t>1,35; 3,12</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1316,27 +1316,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1369,27 +1369,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>2215</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1494</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1301</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2215</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3300</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4620</t>
+          <t>631; 6182</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4548</t>
+          <t>849; 7501</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>629; 6119</t>
+          <t>0; 5205</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>836; 7467</t>
+          <t>0; 4656</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1390; 8005</t>
+          <t>1397; 8468</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1965; 10463</t>
+          <t>1581; 9023</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4003</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1882</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1925</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3773</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4003</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>596; 5058</t>
+          <t>0; 3850</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>608; 5890</t>
+          <t>1950; 8147</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1304; 8101</t>
+          <t>0; 2745</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2891</t>
+          <t>596; 5068</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1946; 8343</t>
+          <t>607; 5207</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3060</t>
+          <t>1793; 7637</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>644; 6388</t>
+          <t>643; 6706</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2665; 10747</t>
+          <t>2702; 10468</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1868; 8570</t>
+          <t>1854; 8263</t>
         </is>
       </c>
     </row>
@@ -1642,27 +1642,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>3403</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1386</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2646</t>
+          <t>0; 3274</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1117; 7041</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4894</t>
+          <t>0; 5076</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3599</t>
+          <t>0; 3171</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1314; 8205</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3347</t>
+          <t>0; 4841</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3885</t>
+          <t>0; 4457</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1121; 7545</t>
+          <t>1112; 7336</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>656; 5847</t>
+          <t>648; 5766</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2204</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1477</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>873</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2464</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2644</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2204</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1477</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5147</t>
+          <t>642; 5857</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>742; 6605</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>729; 7629</t>
+          <t>0; 5075</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>643; 5651</t>
+          <t>0; 4394</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>748; 7062</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5181</t>
+          <t>731; 6944</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>709; 7572</t>
+          <t>701; 7165</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>746; 6567</t>
+          <t>747; 7155</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1491; 8803</t>
+          <t>1461; 9523</t>
         </is>
       </c>
     </row>
@@ -1968,27 +1968,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6153</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>3387</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>9286</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>9104</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6218</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>6153</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1237; 7453</t>
+          <t>1331; 7935</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5259; 15848</t>
+          <t>2800; 11351</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5262; 16245</t>
+          <t>2440; 11413</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1299; 8508</t>
+          <t>1255; 7349</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2848; 11619</t>
+          <t>5329; 15840</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2859; 11704</t>
+          <t>5089; 15050</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3505; 12640</t>
+          <t>3427; 12413</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9716; 22836</t>
+          <t>10200; 22903</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9037; 23031</t>
+          <t>9859; 22801</t>
         </is>
       </c>
     </row>
